--- a/DSA_sheet.xlsx
+++ b/DSA_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B36636-5A62-43CE-9058-F9E1B8193CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B992302-8BA6-4B84-BDF4-1177382A7EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E1FBF9E-BD98-4A07-9410-69C1E7B96CBE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="254">
   <si>
     <t>topic name</t>
   </si>
@@ -835,6 +835,9 @@
   </si>
   <si>
     <t>28-6-26</t>
+  </si>
+  <si>
+    <t>jun</t>
   </si>
 </sst>
 </file>
@@ -895,15 +898,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <u/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -942,6 +936,13 @@
       <u/>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1010,18 +1011,20 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -7927,9 +7930,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
+      <xdr:colOff>212037</xdr:colOff>
       <xdr:row>170</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:rowOff>3968</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="213360" cy="140852"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
@@ -7947,7 +7950,7 @@
           </xdr14:nvContentPartPr>
           <xdr14:nvPr macro=""/>
           <xdr14:xfrm>
-            <a:off x="5013960" y="51282600"/>
+            <a:off x="5149293" y="51303571"/>
             <a:ext cx="213360" cy="140852"/>
           </xdr14:xfrm>
         </xdr:contentPart>
@@ -9184,6 +9187,2466 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="213360" cy="140852"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId135">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="134" name="Ink 133">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5EDC8AE-F148-41EA-884B-1F41B306344A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5128260" y="65524380"/>
+            <a:ext cx="213360" cy="140852"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039E8511-4700-284B-6CCC-B50C091E634C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4920840" y="25206240"/>
+              <a:ext cx="239040" cy="163800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="213360" cy="140852"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId136">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="135" name="Ink 134">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81158949-0006-4EB4-A0E4-2F00F7E6E58A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5128260" y="65966340"/>
+            <a:ext cx="213360" cy="140852"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039E8511-4700-284B-6CCC-B50C091E634C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4920840" y="25206240"/>
+              <a:ext cx="239040" cy="163800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>151140</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>37785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371553</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>226710</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="136" name="Star: 5 Points 135">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{364C47DD-5628-4EDF-B657-EC7A6403DA6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5699256" y="42029653"/>
+          <a:ext cx="220413" cy="188925"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>151140</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>264495</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371553</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>170032</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="137" name="Star: 5 Points 136">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EACF17A4-A0E9-4A29-9AB4-34F134A825C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5699256" y="42256363"/>
+          <a:ext cx="220413" cy="188925"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>138545</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>358958</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>6297</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="138" name="Star: 5 Points 137">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA19BD47-CFDA-4602-891B-97CFF0DE0C12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5686661" y="42457884"/>
+          <a:ext cx="220413" cy="188925"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>25190</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>157437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>245603</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>163734</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="139" name="Star: 5 Points 138">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB3F283A-F628-44E5-B337-1610519A3B68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5573306" y="42615321"/>
+          <a:ext cx="220413" cy="188925"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>151140</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>207819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371553</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>170033</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="140" name="Star: 5 Points 139">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E792614-770A-48FA-8AB0-7A9ECC83BEAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5699256" y="43578844"/>
+          <a:ext cx="220413" cy="188925"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>201522</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>25190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>327472</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="141" name="Star: 5 Points 140">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{943A4FB1-F08E-4452-ABDE-CC201E215408}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5749638" y="43805554"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>220414</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>346364</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>251900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="142" name="Star: 5 Points 141">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F281606D-A9F6-46C1-8739-100F095EEE53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5768530" y="44101537"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>258199</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>56678</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>384149</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>170033</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="143" name="Star: 5 Points 142">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{691AB16D-DBF9-4AD3-A60A-A78C3C9A7B4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5806315" y="44384926"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>251901</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>113356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>377851</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>226711</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="144" name="Star: 5 Points 143">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AC35A58-65EC-406A-AD81-D03334F4C35B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5800017" y="46299373"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>258198</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>125950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>384148</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>239305</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="145" name="Star: 5 Points 144">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9C2CF80-B78A-45C6-A2BE-82E6E958A639}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5806314" y="46677223"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>251900</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>37785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>377850</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>151140</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="146" name="Star: 5 Points 145">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50A7A0B3-65E7-408A-8CA0-813DE82BE128}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5800016" y="46954314"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>245604</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>188925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371554</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>302280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="147" name="Star: 5 Points 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EB17E9B-663F-4E6B-8371-C4E8115409BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5793720" y="47288082"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>233008</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>12595</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>358958</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>125950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="148" name="Star: 5 Points 147">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23FD670-F122-4768-BC66-2E34DD7A336A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5781124" y="44706099"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>220413</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>25190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>346363</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="149" name="Star: 5 Points 148">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF699200-C004-4E07-A5FE-F02AEE666277}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5768529" y="44901322"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>163736</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>31488</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>289686</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>144843</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="150" name="Star: 5 Points 149">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58BFD9F5-D095-45F5-955E-CD38FA5AB247}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5711852" y="49504810"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>151141</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>12595</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="213360" cy="140852"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId137">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="151" name="Ink 150">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A762A397-9118-4296-9B62-4CC3C6CF7BF2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5088397" y="49485917"/>
+            <a:ext cx="213360" cy="140852"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039E8511-4700-284B-6CCC-B50C091E634C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4920840" y="25206240"/>
+              <a:ext cx="239040" cy="163800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>170034</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="213360" cy="140852"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId138">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="152" name="Ink 151">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D981656-F38F-4EAD-AC7E-E48B30F3D0F5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5107290" y="51620776"/>
+            <a:ext cx="213360" cy="140852"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039E8511-4700-284B-6CCC-B50C091E634C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4920840" y="25206240"/>
+              <a:ext cx="239040" cy="163800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>176330</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>302280</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>251900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="153" name="Star: 5 Points 152">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A5C9F74-7F99-4B55-9BE9-0D51D930226F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5724446" y="51620776"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>233008</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>31488</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>358958</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>144843</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="154" name="Star: 5 Points 153">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B8C167C-89BA-4493-B03C-388235BB7824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5781124" y="50417951"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>226711</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>163735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>352661</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>277090</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="155" name="Star: 5 Points 154">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50D05A35-11C6-47EC-A2EC-BCAAAE5FA860}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5774827" y="50732826"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>264496</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>119652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>390446</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>233007</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="156" name="Star: 5 Points 155">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79065F89-A95D-4EE3-B025-13580E6702D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5812612" y="51053999"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>277091</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>37785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>403041</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>151140</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="157" name="Star: 5 Points 156">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57AE7DEF-B18C-4CD5-A2EE-40A7C33B19F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5825207" y="51337388"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>195223</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>37785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>321173</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>151140</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="158" name="Star: 5 Points 157">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB98225B-7BFE-4E94-9C62-00083342022F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5743339" y="22715157"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>251901</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>50380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>377851</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>163735</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="159" name="Star: 5 Points 158">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{803F4111-3F81-4FF2-8214-2ED4DF980EB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5800017" y="22910380"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>270793</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>125951</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>396743</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>239306</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="160" name="Star: 5 Points 159">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6692BA0B-4388-4641-8791-6F6E20135C71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5818909" y="23168579"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>289686</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>94463</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>415636</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>207818</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="161" name="Star: 5 Points 160">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D270022-1FA9-4FD4-A212-8CAFAF91156B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5837802" y="23521240"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>214116</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>340066</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>182628</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="163" name="Star: 5 Points 162">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08D3623B-50BF-4049-9B3B-BE7F7537AD69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5762232" y="24591818"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>314876</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>157438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>440826</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>270793</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="164" name="Star: 5 Points 163">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{676A9D85-6618-4EB1-AA2D-8137998068A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5862992" y="24862612"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>207819</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>100761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>333769</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>214116</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="165" name="Star: 5 Points 164">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{595FD4B0-823E-4D6D-9E95-40931F04B739}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5755935" y="26241769"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>220414</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>18892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>346364</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>132247</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="162" name="Star: 5 Points 161">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0AA777E-3365-4DAF-87DF-BBB9EAE17B77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5768530" y="25246760"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>245603</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>138546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371553</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>251901</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="166" name="Star: 5 Points 165">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34EF9E70-16EF-46A0-8DB0-ADC441256AD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5793719" y="25549042"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>163736</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>18892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>289686</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>132247</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="167" name="Star: 5 Points 166">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A361CFD-F39B-4249-BBB8-2DFE7288CD05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5711852" y="27620925"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>182629</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>308579</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="168" name="Star: 5 Points 167">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F5D215-709C-4557-9160-5BE3638486F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5730745" y="27419405"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>195223</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>119653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>321173</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>233008</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="169" name="Star: 5 Points 168">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{814DEE18-4E7E-4B24-853E-3CB798632E86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5743339" y="27904314"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>245604</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>119653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371554</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>233008</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="170" name="Star: 5 Points 169">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF0C8DE6-BBEB-4A8C-8B98-754662604FA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5793720" y="25895405"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>182628</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>107058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>308578</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>220413</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="171" name="Star: 5 Points 170">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC89DE5E-2F3B-4333-9FF0-11DCFF75A6A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5730744" y="30996397"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>201521</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>327471</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>226710</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="172" name="Star: 5 Points 171">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46CFA65A-98A0-4E04-AD70-583D9FB9F7AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5749637" y="31367950"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>220413</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>119653</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>346363</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>233008</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="173" name="Star: 5 Points 172">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28054DB3-3089-47D5-B447-33810379FCB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5768529" y="31739504"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>119653</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>245603</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>251900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="174" name="Star: 5 Points 173">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A1D3931-ABE6-4DB9-9C6A-FF27008F410B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5667769" y="36506727"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11850,6 +14313,118 @@
 </inkml:ink>
 </file>
 
+<file path=xl/ink/ink95.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-07-16T17:12:05.746"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#66CC00"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 141 24575,'0'6'0,"2"1"0,-1 0 0,1 0 0,0-1 0,0 1 0,1-1 0,5 11 0,9 21 0,-17-37 0,23 67 0,-20-61 0,0 0 0,0-1 0,0 0 0,1 0 0,0 1 0,1-1 0,8 9 0,-8-12 0,0 0 0,0-1 0,0 1 0,-1-1 0,2-1 0,-1 0 0,0 0 0,1 1 0,-2-1 0,2-1 0,-1 1 0,1-1 0,0 0 0,-2-1 0,2 1 0,-1-1 0,1 0 0,-1 0 0,0-1 0,0 2 0,0-2 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,4-4 0,42-50 0,-36 38 0,2 0 0,0 1 0,1 1 0,36-27 0,-45 38 0,0-2 0,-1 2 0,0-2 0,13-16 0,-13 14 0,0 2 0,0-1 0,15-11 0,-16 15-136,1-1-1,-1 0 1,-1 0-1,0 1 1,0-2-1,0 0 1,0 0-1,-2 0 0,8-13 1,-8 7-6690</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink96.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-07-16T17:39:03.769"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#66CC00"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 141 24575,'0'6'0,"2"1"0,-1 0 0,1 0 0,0-1 0,0 1 0,1-1 0,5 11 0,9 21 0,-17-37 0,23 67 0,-20-61 0,0 0 0,0-1 0,0 0 0,1 0 0,0 1 0,1-1 0,8 9 0,-8-12 0,0 0 0,0-1 0,0 1 0,-1-1 0,2-1 0,-1 0 0,0 0 0,1 1 0,-2-1 0,2-1 0,-1 1 0,1-1 0,0 0 0,-2-1 0,2 1 0,-1-1 0,1 0 0,-1 0 0,0-1 0,0 2 0,0-2 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,4-4 0,42-50 0,-36 38 0,2 0 0,0 1 0,1 1 0,36-27 0,-45 38 0,0-2 0,-1 2 0,0-2 0,13-16 0,-13 14 0,0 2 0,0-1 0,15-11 0,-16 15-136,1-1-1,-1 0 1,-1 0-1,0 1 1,0-2-1,0 0 1,0 0-1,-2 0 0,8-13 1,-8 7-6690</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink97.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-07-20T14:25:12.855"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#66CC00"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 141 24575,'0'6'0,"2"1"0,-1 0 0,1 0 0,0-1 0,0 1 0,1-1 0,5 11 0,9 21 0,-17-37 0,23 67 0,-20-61 0,0 0 0,0-1 0,0 0 0,1 0 0,0 1 0,1-1 0,8 9 0,-8-12 0,0 0 0,0-1 0,0 1 0,-1-1 0,2-1 0,-1 0 0,0 0 0,1 1 0,-2-1 0,2-1 0,-1 1 0,1-1 0,0 0 0,-2-1 0,2 1 0,-1-1 0,1 0 0,-1 0 0,0-1 0,0 2 0,0-2 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,4-4 0,42-50 0,-36 38 0,2 0 0,0 1 0,1 1 0,36-27 0,-45 38 0,0-2 0,-1 2 0,0-2 0,13-16 0,-13 14 0,0 2 0,0-1 0,15-11 0,-16 15-136,1-1-1,-1 0 1,-1 0-1,0 1 1,0-2-1,0 0 1,0 0-1,-2 0 0,8-13 1,-8 7-6690</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink98.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-07-21T14:32:50.010"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#66CC00"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 141 24575,'0'6'0,"2"1"0,-1 0 0,1 0 0,0-1 0,0 1 0,1-1 0,5 11 0,9 21 0,-17-37 0,23 67 0,-20-61 0,0 0 0,0-1 0,0 0 0,1 0 0,0 1 0,1-1 0,8 9 0,-8-12 0,0 0 0,0-1 0,0 1 0,-1-1 0,2-1 0,-1 0 0,0 0 0,1 1 0,-2-1 0,2-1 0,-1 1 0,1-1 0,0 0 0,-2-1 0,2 1 0,-1-1 0,1 0 0,-1 0 0,0-1 0,0 2 0,0-2 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,4-4 0,42-50 0,-36 38 0,2 0 0,0 1 0,1 1 0,36-27 0,-45 38 0,0-2 0,-1 2 0,0-2 0,13-16 0,-13 14 0,0 2 0,0-1 0,15-11 0,-16 15-136,1-1-1,-1 0 1,-1 0-1,0 1 1,0-2-1,0 0 1,0 0-1,-2 0 0,8-13 1,-8 7-6690</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -12682,8 +15257,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="C79" s="13" t="s">
+    <row r="79" spans="2:7" ht="21" x14ac:dyDescent="0.4">
+      <c r="C79" s="12" t="s">
         <v>81</v>
       </c>
     </row>
@@ -12741,7 +15316,7 @@
       </c>
     </row>
     <row r="87" spans="3:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="D87" s="14" t="s">
+      <c r="D87" s="13" t="s">
         <v>89</v>
       </c>
       <c r="G87" s="9">
@@ -12815,7 +15390,7 @@
       </c>
     </row>
     <row r="97" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D97" s="16" t="s">
+      <c r="D97" s="15" t="s">
         <v>99</v>
       </c>
       <c r="G97" s="9">
@@ -12878,7 +15453,7 @@
       </c>
     </row>
     <row r="109" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D109" s="16" t="s">
+      <c r="D109" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G109" s="9">
@@ -13024,7 +15599,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:7" ht="21" x14ac:dyDescent="0.4">
+      <c r="C136" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="137" spans="3:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
         <v>138</v>
       </c>
@@ -13130,7 +15710,7 @@
       </c>
     </row>
     <row r="152" spans="3:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="D152" s="14" t="s">
+      <c r="D152" s="13" t="s">
         <v>152</v>
       </c>
     </row>
@@ -13202,7 +15782,7 @@
       </c>
     </row>
     <row r="164" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D164" s="8" t="s">
+      <c r="D164" s="19" t="s">
         <v>163</v>
       </c>
     </row>
@@ -13257,6 +15837,9 @@
       <c r="D172" s="8" t="s">
         <v>170</v>
       </c>
+      <c r="G172" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="173" spans="3:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="D173" s="8" t="s">
@@ -13269,7 +15852,7 @@
       </c>
     </row>
     <row r="175" spans="3:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="D175" s="14" t="s">
+      <c r="D175" s="13" t="s">
         <v>173</v>
       </c>
     </row>
@@ -13389,13 +15972,13 @@
       </c>
     </row>
     <row r="199" spans="2:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B199" s="17" t="s">
+      <c r="B199" s="16" t="s">
         <v>197</v>
       </c>
       <c r="C199" t="s">
         <v>87</v>
       </c>
-      <c r="D199" s="15" t="s">
+      <c r="D199" s="14" t="s">
         <v>195</v>
       </c>
     </row>
@@ -13528,11 +16111,17 @@
       <c r="D216" s="8" t="s">
         <v>213</v>
       </c>
+      <c r="G216" s="9">
+        <v>46215</v>
+      </c>
     </row>
     <row r="217" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D217" s="8" t="s">
         <v>214</v>
       </c>
+      <c r="G217" s="9">
+        <v>46219</v>
+      </c>
     </row>
     <row r="218" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D218" s="8" t="s">
@@ -13580,10 +16169,10 @@
       <c r="G224" s="9">
         <v>46211</v>
       </c>
-      <c r="J224" s="18"/>
+      <c r="J224" s="17"/>
     </row>
     <row r="225" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D225" s="19" t="s">
+      <c r="D225" s="18" t="s">
         <v>221</v>
       </c>
       <c r="G225" s="9">

--- a/DSA_sheet.xlsx
+++ b/DSA_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B992302-8BA6-4B84-BDF4-1177382A7EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFC5105-715E-4493-9477-BD34DF3F3222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E1FBF9E-BD98-4A07-9410-69C1E7B96CBE}"/>
   </bookViews>
@@ -844,7 +844,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -947,8 +947,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -979,6 +987,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -993,7 +1007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1026,6 +1040,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -11647,6 +11664,1446 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="175" name="Star: 5 Points 174">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AFCA39B-C08B-4B56-B3CA-F7098D086F16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="61199306"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="176" name="Star: 5 Points 175">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CACF1D1-609E-42D1-9F7E-454FB35FA2F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="61381934"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="177" name="Star: 5 Points 176">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9A2532C-07F8-4D89-922C-F30C54531E14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="61564562"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="178" name="Star: 5 Points 177">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E9A473-77AB-46F9-A2BD-3D7080DF9F79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="61747190"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="179" name="Star: 5 Points 178">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B6E4E84-BBEB-44EB-B4F7-3AD975CFB9E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="61929818"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="180" name="Star: 5 Points 179">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A93E8BA-5117-46B7-8C2A-48AAAFEF5389}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="62295074"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>205</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>205</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="181" name="Star: 5 Points 180">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98FAF6F9-24F3-4D80-AB4E-92BD0CF5DF54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="62660331"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="182" name="Star: 5 Points 181">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E028FDE-FA75-42AB-A1D7-08B84FFDBE81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="63025587"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="183" name="Star: 5 Points 182">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{563D9417-57F7-4781-8844-B3C0B0C6F3D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="63208215"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="184" name="Star: 5 Points 183">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15625011-2C28-4C3B-9338-B71CB527CE41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="63756099"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="185" name="Star: 5 Points 184">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3923127-E2CF-4DCE-946C-0D6709B2348A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="63756099"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>365256</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="186" name="Star: 5 Points 185">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E1304DE-74F3-4EF9-A64E-B8D4D1CF6175}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="64303983"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="187" name="Star: 5 Points 186">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E4390DE-A7D6-4715-96C4-819C7B6CD867}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="64669240"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="188" name="Star: 5 Points 187">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5115898-91AB-4C6F-8741-537074CDFBD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="65034496"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="189" name="Star: 5 Points 188">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DC934C5-FAC1-4E53-A117-ABB3E5191929}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="65399752"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="190" name="Star: 5 Points 189">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30A017C5-AA6A-40D9-8B27-2C57D965C1D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="65947636"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="191" name="Star: 5 Points 190">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{389A0266-F380-4CB0-A73A-6A07E606AF71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="65582380"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="192" name="Star: 5 Points 191">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AC7EC3F-1B5B-4DA1-92DD-25939B103967}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="67043405"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>221</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>221</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="193" name="Star: 5 Points 192">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F15B2B3-3E14-4055-8694-519146EF472D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="67408661"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="194" name="Star: 5 Points 193">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC4C30E-A7BB-4620-81E2-F751EE444150}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="67773917"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>182628</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="195" name="Star: 5 Points 194">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{018E07A0-F69A-41A1-9E8C-47C16432C19D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="67956545"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="196" name="Star: 5 Points 195">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3365F27-A164-4918-B0BC-A4B285B95196}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="68321802"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>125950</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>113355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="197" name="Star: 5 Points 196">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2CB4FD8-A254-429E-AE98-9261A63137EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5548116" y="68504430"/>
+          <a:ext cx="125950" cy="113355"/>
+        </a:xfrm>
+        <a:prstGeom prst="star5">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="213360" cy="140852"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId139">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="198" name="Ink 197">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93C587B9-7FC0-4723-8776-CC3BDB539EE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="4937256" y="68504430"/>
+            <a:ext cx="213360" cy="140852"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039E8511-4700-284B-6CCC-B50C091E634C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4920840" y="25206240"/>
+              <a:ext cx="239040" cy="163800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -14425,6 +15882,34 @@
 </inkml:ink>
 </file>
 
+<file path=xl/ink/ink99.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-07-27T12:12:25.755"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#66CC00"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 141 24575,'0'6'0,"2"1"0,-1 0 0,1 0 0,0-1 0,0 1 0,1-1 0,5 11 0,9 21 0,-17-37 0,23 67 0,-20-61 0,0 0 0,0-1 0,0 0 0,1 0 0,0 1 0,1-1 0,8 9 0,-8-12 0,0 0 0,0-1 0,0 1 0,-1-1 0,2-1 0,-1 0 0,0 0 0,1 1 0,-2-1 0,2-1 0,-1 1 0,1-1 0,0 0 0,-2-1 0,2 1 0,-1-1 0,1 0 0,-1 0 0,0-1 0,0 2 0,0-2 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0 0,4-4 0,42-50 0,-36 38 0,2 0 0,0 1 0,1 1 0,36-27 0,-45 38 0,0-2 0,-1 2 0,0-2 0,13-16 0,-13 14 0,0 2 0,0-1 0,15-11 0,-16 15-136,1-1-1,-1 0 1,-1 0-1,0 1 1,0-2-1,0 0 1,0 0-1,-2 0 0,8-13 1,-8 7-6690</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -16180,8 +17665,11 @@
       </c>
     </row>
     <row r="226" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D226" s="8" t="s">
+      <c r="D226" s="20" t="s">
         <v>222</v>
+      </c>
+      <c r="G226" s="9">
+        <v>46213</v>
       </c>
     </row>
     <row r="227" spans="4:7" x14ac:dyDescent="0.3">
